--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_V007.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_V007.xlsx
@@ -25817,7 +25817,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>18d8f2802debcbc06cca471c291f6b513e298dfbff9ca8797a5c3be711cded88</t>
+          <t>60ec4d101de723d8022073123c44f9391887d602251d229b8c1329ae7b245f14</t>
         </is>
       </c>
     </row>
